--- a/outputs/tables/reverse_scoring_descriptives.xlsx
+++ b/outputs/tables/reverse_scoring_descriptives.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Before_and_after" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Factor_reverse_means" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">stage</t>
   </si>
@@ -114,6 +115,36 @@
   </si>
   <si>
     <t xml:space="preserve">competence_ET_2_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">original_variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reversed_variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_mean_after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">difference_from_expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reverse_check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
   </si>
 </sst>
 </file>
@@ -174,6 +205,24 @@
     <tableColumn id="8" name="median"/>
     <tableColumn id="9" name="min"/>
     <tableColumn id="10" name="max"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:I12" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I12"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="original_variable"/>
+    <tableColumn id="2" name="reversed_variable"/>
+    <tableColumn id="3" name="n_before"/>
+    <tableColumn id="4" name="n_after"/>
+    <tableColumn id="5" name="mean_before"/>
+    <tableColumn id="6" name="mean_after"/>
+    <tableColumn id="7" name="expected_mean_after"/>
+    <tableColumn id="8" name="difference_from_expected"/>
+    <tableColumn id="9" name="reverse_check"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1216,4 +1265,377 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="24.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.29397192402973</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.70602807597027</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.70602807597027</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.63088356729975</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.36911643270025</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.36911643270025</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.64987613542527</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.35012386457473</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.35012386457473</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.94302229562345</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.05697770437655</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.05697770437655</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.30222956234517</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.69777043765483</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.69777043765483</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.12386457473163</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.87613542526837</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.87613542526837</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.01403798513625</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.98596201486375</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.98596201486375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.02725020644096</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.97274979355904</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.97274979355904</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.12469033856317</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.87530966143683</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.87530966143683</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.58794384805946</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.41205615194054</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.41205615194054</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.88934764657308</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.11065235342692</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.11065235342692</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
 </file>